--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Private Bank ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Private Bank ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Private Bank ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,33 +61,33 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
     <t>INE237A01028</t>
   </si>
   <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>IndusInd Bank Ltd.</t>
   </si>
   <si>
@@ -106,18 +106,18 @@
     <t>INE092T01019</t>
   </si>
   <si>
+    <t>Yes Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE528G01035</t>
+  </si>
+  <si>
     <t>Bandhan Bank Ltd.</t>
   </si>
   <si>
     <t>INE545U01014</t>
   </si>
   <si>
-    <t>City Union Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE491A01021</t>
-  </si>
-  <si>
     <t>RBL Bank Ltd.</t>
   </si>
   <si>
@@ -172,15 +172,6 @@
     <t>Total Net Assets</t>
   </si>
   <si>
-    <t>Details of the Equity shares have been lent under Securities Lending and Borrowing as follows:-</t>
-  </si>
-  <si>
-    <t>Name of the Instrument</t>
-  </si>
-  <si>
-    <t>RBL Bank Ltd</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -190,7 +181,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -217,7 +208,7 @@
     <numFmt numFmtId="178" formatCode="##0.00%"/>
     <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -233,18 +224,6 @@
       <sz val="8.25"/>
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -305,7 +284,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -391,20 +370,6 @@
         <color auto="1"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -431,44 +396,44 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -495,38 +460,17 @@
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -623,13 +567,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -647,7 +591,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="12992100"/>
+          <a:off x="666750" y="12420600"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -662,13 +606,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -686,7 +630,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15849600"/>
+          <a:off x="666750" y="15278100"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1020,19 +964,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J79"/>
+  <dimension ref="B1:J76"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="27" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="27" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="27" width="16.285714285714285" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="27" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="27" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="27" width="11.0" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="27" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="27" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="27" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="27" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.285714285714285" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1120,10 +1064,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>299166.85000000003</v>
+        <v>335673.00999999995</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9999709283764</v>
+        <v>0.9999744669068998</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1157,10 +1101,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>299166.85000000003</v>
+        <v>335673.00999999995</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9999709283764</v>
+        <v>0.9999744669068998</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1183,13 +1127,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>3497652</v>
+        <v>4970250</v>
       </c>
       <c r="G8" s="15">
-        <v>66500.86</v>
+        <v>71859.87</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2222803987542</v>
+        <v>0.214071531087</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1212,13 +1156,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>4904007</v>
+        <v>3666595</v>
       </c>
       <c r="G9" s="15">
-        <v>61437.40</v>
+        <v>71311.61</v>
       </c>
       <c r="H9" s="16">
-        <v>0.2053556866847</v>
+        <v>0.2124382570825</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1241,13 +1185,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>3552812</v>
+        <v>5472492</v>
       </c>
       <c r="G10" s="15">
-        <v>60353.39</v>
+        <v>65243.05</v>
       </c>
       <c r="H10" s="16">
-        <v>0.2017323624893</v>
+        <v>0.1943599342203</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1270,13 +1214,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>5694002</v>
+        <v>2820856</v>
       </c>
       <c r="G11" s="15">
-        <v>56148.55</v>
+        <v>58524.30</v>
       </c>
       <c r="H11" s="16">
-        <v>0.1876776042215</v>
+        <v>0.174344686496</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1299,13 +1243,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>1950772</v>
+        <v>2127647</v>
       </c>
       <c r="G12" s="15">
-        <v>19336.05</v>
+        <v>17381.81</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0646311176176</v>
+        <v>0.051780648639599997</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1328,13 +1272,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>7226786</v>
+        <v>7920894</v>
       </c>
       <c r="G13" s="15">
-        <v>13529.27</v>
+        <v>16004.96</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0452218442055</v>
+        <v>0.0476789937441</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1357,13 +1301,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>18278198</v>
+        <v>20029622</v>
       </c>
       <c r="G14" s="15">
-        <v>11559.13</v>
+        <v>13614.13</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0386366135062</v>
+        <v>0.0405566786235</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1386,13 +1330,13 @@
         <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>2453399</v>
+        <v>60911780</v>
       </c>
       <c r="G15" s="15">
-        <v>3713.96</v>
+        <v>13083.85</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0124139824621</v>
+        <v>0.0389769672838</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1415,13 +1359,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>2126846</v>
+        <v>2683869</v>
       </c>
       <c r="G16" s="15">
-        <v>3694.76</v>
+        <v>4567.68</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0123498060942</v>
+        <v>0.013607180908</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1444,13 +1388,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>1756073</v>
+        <v>1915683</v>
       </c>
       <c r="G17" s="15">
-        <v>2893.48</v>
+        <v>4081.75</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0096715123411</v>
+        <v>0.0121595888221</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1965,10 +1909,10 @@
         <v>13</v>
       </c>
       <c r="G45" s="9">
-        <v>80.42</v>
+        <v>52.36</v>
       </c>
       <c r="H45" s="10">
-        <v>0.0002688053909</v>
+        <v>0.0001559811528</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>13</v>
@@ -2002,10 +1946,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="18">
-        <v>-71.72248120000586</v>
+        <v>-43.78901109995786</v>
       </c>
       <c r="H47" s="19">
-        <v>-0.00023973376766528307</v>
+        <v>-0.00013044806024494336</v>
       </c>
       <c r="I47" s="18" t="s">
         <v>13</v>
@@ -2031,10 +1975,10 @@
         <v>13</v>
       </c>
       <c r="G48" s="18">
-        <v>299175.5475188</v>
+        <v>335681.5809889</v>
       </c>
       <c r="H48" s="19">
-        <v>0.9999999999996346</v>
+        <v>0.999999999999455</v>
       </c>
       <c r="I48" s="18" t="s">
         <v>13</v>
@@ -2043,121 +1987,99 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="15" customHeight="1">
-      <c r="B50" s="21" t="s">
+    <row r="51" spans="2:9" ht="15" customHeight="1">
+      <c r="B51" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="22"/>
-    </row>
-    <row r="51" spans="2:3" ht="15" customHeight="1">
-      <c r="B51" s="23" t="s">
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+    </row>
+    <row r="52" spans="2:8" ht="15" customHeight="1">
+      <c r="B52" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" ht="15" customHeight="1">
-      <c r="B52" s="25" t="s">
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+    </row>
+    <row r="53" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B53" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="26">
-        <v>232390</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" ht="15" customHeight="1">
-      <c r="B54" s="13" t="s">
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+    </row>
+    <row r="54" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B54" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-    </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
-      <c r="B55" s="13" t="s">
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+    </row>
+    <row r="55" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B55" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-    </row>
-    <row r="56" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B56" s="28" t="s">
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+    </row>
+    <row r="57" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B57" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-    </row>
-    <row r="57" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B57" s="28" t="s">
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+    </row>
+    <row r="60" ht="15">
+      <c r="B60" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-    </row>
-    <row r="58" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B58" s="28" t="s">
+    </row>
+    <row r="75" ht="15">
+      <c r="B75" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-    </row>
-    <row r="60" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B60" s="28" t="s">
+    </row>
+    <row r="76" ht="15">
+      <c r="B76" s="21" t="s">
         <v>60</v>
-      </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-    </row>
-    <row r="63" ht="15">
-      <c r="B63" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" ht="15">
-      <c r="B78" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" ht="15">
-      <c r="B79" s="27" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B60:H60"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B52:H52"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
